--- a/samples/예시데이터_기술지원DB.xlsx
+++ b/samples/예시데이터_기술지원DB.xlsx
@@ -402,7 +402,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I6"/>
+  <dimension ref="A1:K6"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -432,6 +432,12 @@
       <c r="I1" t="str">
         <v>system_cat</v>
       </c>
+      <c r="J1" t="str">
+        <v>action_content</v>
+      </c>
+      <c r="K1" t="str">
+        <v>complete_date</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
@@ -461,6 +467,12 @@
       <c r="I2" t="str">
         <v>Engine</v>
       </c>
+      <c r="J2" t="str">
+        <v>(예시) 스텝핑 모터 커넥터 접촉 불량 확인 — 커넥터 재체결 후 에러코드 219 해제, 조향 정상 확인.</v>
+      </c>
+      <c r="K2" t="str">
+        <v>2026-09-09</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
@@ -490,6 +502,12 @@
       <c r="I3" t="str">
         <v>Engine</v>
       </c>
+      <c r="J3" t="str">
+        <v/>
+      </c>
+      <c r="K3" t="str">
+        <v/>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
@@ -519,6 +537,12 @@
       <c r="I4" t="str">
         <v>Drive Axle</v>
       </c>
+      <c r="J4" t="str">
+        <v/>
+      </c>
+      <c r="K4" t="str">
+        <v/>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
@@ -548,6 +572,12 @@
       <c r="I5" t="str">
         <v>Hydraulic</v>
       </c>
+      <c r="J5" t="str">
+        <v/>
+      </c>
+      <c r="K5" t="str">
+        <v/>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
@@ -577,10 +607,16 @@
       <c r="I6" t="str">
         <v>Electric</v>
       </c>
+      <c r="J6" t="str">
+        <v/>
+      </c>
+      <c r="K6" t="str">
+        <v/>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I6"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K6"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/samples/예시데이터_기술지원DB.xlsx
+++ b/samples/예시데이터_기술지원DB.xlsx
@@ -9,6 +9,7 @@
     <sheet name="사용자" sheetId="4" r:id="rId4"/>
     <sheet name="소스등록" sheetId="5" r:id="rId5"/>
     <sheet name="Log Data" sheetId="6" r:id="rId6"/>
+    <sheet name="메일" sheetId="7" r:id="rId7"/>
   </sheets>
 </workbook>
 </file>
@@ -402,7 +403,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K6"/>
+  <dimension ref="A1:L6"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -438,6 +439,9 @@
       <c r="K1" t="str">
         <v>complete_date</v>
       </c>
+      <c r="L1" t="str">
+        <v>complete_image</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
@@ -473,6 +477,9 @@
       <c r="K2" t="str">
         <v>2026-09-09</v>
       </c>
+      <c r="L2" t="str">
+        <v>202609080001_C1.jpg</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
@@ -508,6 +515,9 @@
       <c r="K3" t="str">
         <v/>
       </c>
+      <c r="L3" t="str">
+        <v/>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
@@ -543,6 +553,9 @@
       <c r="K4" t="str">
         <v/>
       </c>
+      <c r="L4" t="str">
+        <v/>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
@@ -578,6 +591,9 @@
       <c r="K5" t="str">
         <v/>
       </c>
+      <c r="L5" t="str">
+        <v/>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
@@ -613,10 +629,13 @@
       <c r="K6" t="str">
         <v/>
       </c>
+      <c r="L6" t="str">
+        <v/>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K6"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L6"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -922,7 +941,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:M7"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -952,6 +971,18 @@
       <c r="I1" t="str">
         <v>territory_cd</v>
       </c>
+      <c r="J1" t="str">
+        <v>approval</v>
+      </c>
+      <c r="K1" t="str">
+        <v>approved_by</v>
+      </c>
+      <c r="L1" t="str">
+        <v>approved_date</v>
+      </c>
+      <c r="M1" t="str">
+        <v>manage_territory</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
@@ -981,6 +1012,18 @@
       <c r="I2" t="str">
         <v>경기</v>
       </c>
+      <c r="J2" t="str">
+        <v>Approved</v>
+      </c>
+      <c r="K2" t="str">
+        <v>demo_admin</v>
+      </c>
+      <c r="L2" t="str">
+        <v>2026-07-30</v>
+      </c>
+      <c r="M2" t="str">
+        <v/>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
@@ -1010,6 +1053,18 @@
       <c r="I3" t="str">
         <v>경남</v>
       </c>
+      <c r="J3" t="str">
+        <v>Approved</v>
+      </c>
+      <c r="K3" t="str">
+        <v>demo_admin</v>
+      </c>
+      <c r="L3" t="str">
+        <v>2026-08-14</v>
+      </c>
+      <c r="M3" t="str">
+        <v/>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
@@ -1039,6 +1094,18 @@
       <c r="I4" t="str">
         <v>Europe</v>
       </c>
+      <c r="J4" t="str">
+        <v>Approved</v>
+      </c>
+      <c r="K4" t="str">
+        <v>demo_admin_gl</v>
+      </c>
+      <c r="L4" t="str">
+        <v>2026-08-19</v>
+      </c>
+      <c r="M4" t="str">
+        <v/>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
@@ -1068,10 +1135,104 @@
       <c r="I5" t="str">
         <v>Direct Sales</v>
       </c>
+      <c r="J5" t="str">
+        <v>Approved</v>
+      </c>
+      <c r="K5" t="str">
+        <v>(첫 관리자 자동 승인)</v>
+      </c>
+      <c r="L5" t="str">
+        <v>2026-06-30</v>
+      </c>
+      <c r="M5" t="str">
+        <v>경기; 경남; 전라; 충청; 강원; Direct Sales</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>demo_admin_gl</v>
+      </c>
+      <c r="B6" t="str">
+        <v>예시 해외PS담당자</v>
+      </c>
+      <c r="C6" t="str">
+        <v>ps-global@example.com</v>
+      </c>
+      <c r="D6" t="str">
+        <v>010-0000-0008</v>
+      </c>
+      <c r="E6" t="str">
+        <v>KR</v>
+      </c>
+      <c r="F6" t="str">
+        <v>본사 PS팀(예시)</v>
+      </c>
+      <c r="G6" t="str">
+        <v>2026-07-10</v>
+      </c>
+      <c r="H6" t="str">
+        <v>ADMIN</v>
+      </c>
+      <c r="I6" t="str">
+        <v>Direct Sales</v>
+      </c>
+      <c r="J6" t="str">
+        <v>Approved</v>
+      </c>
+      <c r="K6" t="str">
+        <v>demo_admin</v>
+      </c>
+      <c r="L6" t="str">
+        <v>2026-07-10</v>
+      </c>
+      <c r="M6" t="str">
+        <v>Europe; North America; South America; Middle East; Africa; Asia; Oceania</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>demo_new01</v>
+      </c>
+      <c r="B7" t="str">
+        <v>예시 신규정비사</v>
+      </c>
+      <c r="C7" t="str">
+        <v>new01@example.com</v>
+      </c>
+      <c r="D7" t="str">
+        <v>010-0000-0010</v>
+      </c>
+      <c r="E7" t="str">
+        <v>KR</v>
+      </c>
+      <c r="F7" t="str">
+        <v>예시딜러 충청</v>
+      </c>
+      <c r="G7" t="str">
+        <v>2026-09-28</v>
+      </c>
+      <c r="H7" t="str">
+        <v>USER</v>
+      </c>
+      <c r="I7" t="str">
+        <v>충청</v>
+      </c>
+      <c r="J7" t="str">
+        <v>Pending</v>
+      </c>
+      <c r="K7" t="str">
+        <v/>
+      </c>
+      <c r="L7" t="str">
+        <v/>
+      </c>
+      <c r="M7" t="str">
+        <v/>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I5"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:M7"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1206,4 +1367,44 @@
     <ignoredError numberStoredAsText="1" sqref="A1:C6"/>
   </ignoredErrors>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:I1"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>mail_id</v>
+      </c>
+      <c r="B1" t="str">
+        <v>ref_no</v>
+      </c>
+      <c r="C1" t="str">
+        <v>reason</v>
+      </c>
+      <c r="D1" t="str">
+        <v>mail_to</v>
+      </c>
+      <c r="E1" t="str">
+        <v>subject</v>
+      </c>
+      <c r="F1" t="str">
+        <v>body</v>
+      </c>
+      <c r="G1" t="str">
+        <v>created_date</v>
+      </c>
+      <c r="H1" t="str">
+        <v>status</v>
+      </c>
+      <c r="I1" t="str">
+        <v>sent_date</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:I1"/>
+  </ignoredErrors>
+</worksheet>
 </file>
--- a/samples/예시데이터_기술지원DB.xlsx
+++ b/samples/예시데이터_기술지원DB.xlsx
@@ -1239,7 +1239,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:C19"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1285,9 +1285,174 @@
         <v/>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>15/18/20/23BRP-9</v>
+      </c>
+      <c r="B5" t="str">
+        <v>15BRP-9</v>
+      </c>
+      <c r="C5" t="str">
+        <v>BRP-9_OM.pdf; BRP-9_SM</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>15/18/20/23BRP-9</v>
+      </c>
+      <c r="B6" t="str">
+        <v>18BRP-9</v>
+      </c>
+      <c r="C6" t="str">
+        <v>BRP-9_OM.pdf; BRP-9_SM</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>15/18/20/23BRP-9</v>
+      </c>
+      <c r="B7" t="str">
+        <v>20BRP-9</v>
+      </c>
+      <c r="C7" t="str">
+        <v>BRP-9_OM.pdf; BRP-9_SM</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>15/18/20/23BRP-9</v>
+      </c>
+      <c r="B8" t="str">
+        <v>23BRP-9</v>
+      </c>
+      <c r="C8" t="str">
+        <v>BRP-9_OM.pdf; BRP-9_SM</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>15/18/20/23BRP-X</v>
+      </c>
+      <c r="B9" t="str">
+        <v>15BRP-X</v>
+      </c>
+      <c r="C9" t="str">
+        <v>15BRP-X SM_EXP.pdf; 15182023BRP-X OM</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>15/18/20/23BRP-X</v>
+      </c>
+      <c r="B10" t="str">
+        <v>18BRP-X</v>
+      </c>
+      <c r="C10" t="str">
+        <v>15BRP-X SM_EXP.pdf; 15182023BRP-X OM</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>15/18/20/23BRP-X</v>
+      </c>
+      <c r="B11" t="str">
+        <v>20BRP-X</v>
+      </c>
+      <c r="C11" t="str">
+        <v>15BRP-X SM_EXP.pdf; 15182023BRP-X OM</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>15/18/20/23BRP-X</v>
+      </c>
+      <c r="B12" t="str">
+        <v>23BRP-X</v>
+      </c>
+      <c r="C12" t="str">
+        <v>15BRP-X SM_EXP.pdf; 15182023BRP-X OM</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>100D-9V</v>
+      </c>
+      <c r="B13" t="str">
+        <v>100D-9V</v>
+      </c>
+      <c r="C13" t="str">
+        <v>100D-9V OM EXP.pdf; 100D-9V SM ENG</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>25/30/35DE-7</v>
+      </c>
+      <c r="B14" t="str">
+        <v>25DE-7</v>
+      </c>
+      <c r="C14" t="str">
+        <v>253035DE-7 OM; 253035DE-7 SM</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>25/30/35DE-7</v>
+      </c>
+      <c r="B15" t="str">
+        <v>30DE-7</v>
+      </c>
+      <c r="C15" t="str">
+        <v>253035DE-7 OM; 253035DE-7 SM</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>25/30/35DE-7</v>
+      </c>
+      <c r="B16" t="str">
+        <v>35DE-7</v>
+      </c>
+      <c r="C16" t="str">
+        <v>253035DE-7 OM; 253035DE-7 SM</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>25/30/35LE-7</v>
+      </c>
+      <c r="B17" t="str">
+        <v>25LE-7</v>
+      </c>
+      <c r="C17" t="str">
+        <v>253035LE-7 OM; 253035LE-7 SM</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>25/30/35LE-7</v>
+      </c>
+      <c r="B18" t="str">
+        <v>30LE-7</v>
+      </c>
+      <c r="C18" t="str">
+        <v>253035LE-7 OM; 253035LE-7 SM</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>25/30/35LE-7</v>
+      </c>
+      <c r="B19" t="str">
+        <v>35LE-7</v>
+      </c>
+      <c r="C19" t="str">
+        <v>253035LE-7 OM; 253035LE-7 SM</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C19"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/samples/예시데이터_기술지원DB.xlsx
+++ b/samples/예시데이터_기술지원DB.xlsx
@@ -1239,7 +1239,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C19"/>
+  <dimension ref="A1:C34"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1450,9 +1450,174 @@
         <v>253035LE-7 OM; 253035LE-7 SM</v>
       </c>
     </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>22/25/30/32/35B-9</v>
+      </c>
+      <c r="B20" t="str">
+        <v>22B-9</v>
+      </c>
+      <c r="C20" t="str">
+        <v>2225303235B-9_OM; 2225303235B-9_SM</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>22/25/30/32/35B-9</v>
+      </c>
+      <c r="B21" t="str">
+        <v>25B-9</v>
+      </c>
+      <c r="C21" t="str">
+        <v>2225303235B-9_OM; 2225303235B-9_SM</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>22/25/30/32/35B-9</v>
+      </c>
+      <c r="B22" t="str">
+        <v>30B-9</v>
+      </c>
+      <c r="C22" t="str">
+        <v>2225303235B-9_OM; 2225303235B-9_SM</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>22/25/30/32/35B-9</v>
+      </c>
+      <c r="B23" t="str">
+        <v>32B-9</v>
+      </c>
+      <c r="C23" t="str">
+        <v>2225303235B-9_OM; 2225303235B-9_SM</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>22/25/30/32/35B-9</v>
+      </c>
+      <c r="B24" t="str">
+        <v>35B-9</v>
+      </c>
+      <c r="C24" t="str">
+        <v>2225303235B-9_OM; 2225303235B-9_SM</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>25/30/32/35B-9U</v>
+      </c>
+      <c r="B25" t="str">
+        <v>25B-9U</v>
+      </c>
+      <c r="C25" t="str">
+        <v>25303235B-9U_OM; 25303235B-9U_SM</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>25/30/32/35B-9U</v>
+      </c>
+      <c r="B26" t="str">
+        <v>30B-9U</v>
+      </c>
+      <c r="C26" t="str">
+        <v>25303235B-9U_OM; 25303235B-9U_SM</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>25/30/32/35B-9U</v>
+      </c>
+      <c r="B27" t="str">
+        <v>32B-9U</v>
+      </c>
+      <c r="C27" t="str">
+        <v>25303235B-9U_OM; 25303235B-9U_SM</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>25/30/32/35B-9U</v>
+      </c>
+      <c r="B28" t="str">
+        <v>35B-9U</v>
+      </c>
+      <c r="C28" t="str">
+        <v>25303235B-9U_OM; 25303235B-9U_SM</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>15/18/20BCS-9</v>
+      </c>
+      <c r="B29" t="str">
+        <v>15BCS-9</v>
+      </c>
+      <c r="C29" t="str">
+        <v>151820BCS-9_OM; 151820BCS-9_SM</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>15/18/20BCS-9</v>
+      </c>
+      <c r="B30" t="str">
+        <v>18BCS-9</v>
+      </c>
+      <c r="C30" t="str">
+        <v>151820BCS-9_OM; 151820BCS-9_SM</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>15/18/20BCS-9</v>
+      </c>
+      <c r="B31" t="str">
+        <v>20BCS-9</v>
+      </c>
+      <c r="C31" t="str">
+        <v>151820BCS-9_OM; 151820BCS-9_SM</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>15/18/20BCS-9U</v>
+      </c>
+      <c r="B32" t="str">
+        <v>15BCS-9U</v>
+      </c>
+      <c r="C32" t="str">
+        <v>151820BCS-9U OM ENG; 151820BCS-9U SM ENG</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>15/18/20BCS-9U</v>
+      </c>
+      <c r="B33" t="str">
+        <v>18BCS-9U</v>
+      </c>
+      <c r="C33" t="str">
+        <v>151820BCS-9U OM ENG; 151820BCS-9U SM ENG</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v>15/18/20BCS-9U</v>
+      </c>
+      <c r="B34" t="str">
+        <v>20BCS-9U</v>
+      </c>
+      <c r="C34" t="str">
+        <v>151820BCS-9U OM ENG; 151820BCS-9U SM ENG</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C19"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C34"/>
   </ignoredErrors>
 </worksheet>
 </file>
